--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N86_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N86_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.16645927152557</v>
+        <v>6.039549631622905</v>
       </c>
       <c r="D2" t="n">
-        <v>37.03832069903449</v>
+        <v>6.018727113593104</v>
       </c>
       <c r="E2" t="n">
-        <v>20.49660893835589</v>
+        <v>3.330698952482833</v>
       </c>
       <c r="F2" t="n">
-        <v>19.57359740001783</v>
+        <v>3.180709577502898</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.88029388076399</v>
+        <v>5.180547755624149</v>
       </c>
       <c r="D3" t="n">
-        <v>31.66799652586995</v>
+        <v>5.146049435453867</v>
       </c>
       <c r="E3" t="n">
-        <v>20.49660893835589</v>
+        <v>3.330698952482833</v>
       </c>
       <c r="F3" t="n">
-        <v>19.57359740001783</v>
+        <v>3.180709577502898</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.28473966826014</v>
+        <v>4.921270196092274</v>
       </c>
       <c r="D4" t="n">
-        <v>30.78203183113264</v>
+        <v>5.002080172559054</v>
       </c>
       <c r="E4" t="n">
-        <v>20.49660893835589</v>
+        <v>3.330698952482833</v>
       </c>
       <c r="F4" t="n">
-        <v>19.57359740001783</v>
+        <v>3.180709577502898</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>80.07849774491646</v>
+        <v>13.01275588354892</v>
       </c>
       <c r="D5" t="n">
-        <v>78.02673596569424</v>
+        <v>12.67934459442531</v>
       </c>
       <c r="E5" t="n">
-        <v>20.49660893835589</v>
+        <v>3.330698952482833</v>
       </c>
       <c r="F5" t="n">
-        <v>19.57359740001783</v>
+        <v>3.180709577502898</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
